--- a/data/Sep/Tiền trả shop 21Aug-05Sep.xlsx
+++ b/data/Sep/Tiền trả shop 21Aug-05Sep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Sep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21325364-3551-44B4-B87E-5F16DDBDC336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E901C60-0EA6-4039-B60C-7FC9230B306C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
   <si>
     <t>28/8/2026</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>27/8/2026</t>
+  </si>
+  <si>
+    <t>Shop tổng</t>
+  </si>
+  <si>
+    <t>Chênh lệch</t>
   </si>
 </sst>
 </file>
@@ -127,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -150,12 +156,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -169,8 +201,17 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -453,15 +494,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -469,273 +513,338 @@
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>15495</v>
       </c>
-      <c r="D2" s="3">
-        <f t="shared" ref="D2:D3" si="0">SUM(C2)</f>
+      <c r="D2" s="5">
         <v>15495</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="5">
+        <f>D2-C2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>19447</v>
       </c>
-      <c r="D3" s="3">
-        <f t="shared" si="0"/>
+      <c r="D3" s="5">
         <v>19447</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="5">
+        <f>D3-C3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>23499</v>
       </c>
       <c r="D4" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>68977</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23499</v>
+      </c>
+      <c r="E4" s="6">
+        <f>(D4+D5)-(C4+C5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>45478</v>
       </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="5">
+        <v>45478</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>55505</v>
       </c>
       <c r="D6" s="5">
-        <f>SUM(C6:C7)</f>
-        <v>152930</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55505</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" ref="E6" si="0">(D6+D7)-(C6+C7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>97425</v>
       </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="5">
+        <v>97425</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>137136</v>
       </c>
       <c r="D8" s="5">
-        <f>SUM(C8:C9)</f>
-        <v>210572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>137136</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" ref="E8" si="1">(D8+D9)-(C8+C9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>73436</v>
       </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>73436</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
+        <v>129470</v>
+      </c>
+      <c r="D10" s="5">
         <v>128165</v>
       </c>
-      <c r="D10" s="5">
-        <f>SUM(C10:C11)</f>
-        <v>237098</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="6">
+        <f t="shared" ref="E10" si="2">(D10+D11)-(C10+C11)</f>
+        <v>-1305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>108933</v>
       </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="5">
+        <v>108933</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>94202</v>
       </c>
       <c r="D12" s="5">
-        <f>SUM(C12:C13)</f>
-        <v>143185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>94202</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" ref="E12" si="3">(D12+D13)-(C12+C13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>48983</v>
       </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <v>48983</v>
+      </c>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
+        <v>207571</v>
+      </c>
+      <c r="D14" s="5">
         <v>203881</v>
       </c>
-      <c r="D14" s="3">
-        <f>SUM(C14)</f>
-        <v>203881</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="5">
+        <f>D14-C14</f>
+        <v>-3690</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>71312</v>
       </c>
-      <c r="D15" s="3">
-        <f>SUM(C15)</f>
+      <c r="D15" s="5">
         <v>71312</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="5">
+        <f>D15-C15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>57253</v>
       </c>
       <c r="D16" s="5">
-        <f>SUM(C16:C17)</f>
-        <v>80250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57253</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" ref="E16" si="4">(D16+D17)-(C16+C17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>22997</v>
       </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>22997</v>
+      </c>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="4">
         <v>46090</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5">
         <v>7610</v>
       </c>
-      <c r="D18" s="3">
-        <f>SUM(C18)</f>
+      <c r="E18" s="5">
+        <f t="shared" ref="E18:E20" si="5">D18-C18</f>
         <v>7610</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="4">
         <v>46121</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5">
         <v>32599</v>
       </c>
-      <c r="D19" s="3">
-        <f t="shared" ref="D19:D20" si="1">SUM(C19)</f>
+      <c r="E19" s="5">
+        <f t="shared" si="5"/>
         <v>32599</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="4">
         <v>46151</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5">
         <v>64636</v>
       </c>
-      <c r="D20" s="3">
-        <f t="shared" si="1"/>
+      <c r="E20" s="5">
+        <f t="shared" si="5"/>
         <v>64636</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8">
+        <f>SUM(E2:E17)</f>
+        <v>-4995</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
